--- a/bench/data/files/synthetic2_B.xlsx
+++ b/bench/data/files/synthetic2_B.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -549,51 +549,55 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Atlas Ltd</t>
+          <t>Wavelength SA</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2011-01-26</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr"/>
+          <t>2012-06-03</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>2019-04-09</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="n">
-        <v>506.2</v>
+        <v>130</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v/>
+        <v>226.6</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>82.8</v>
+        <v>28.1</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v/>
+        <v>61.1</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>260.3</v>
+        <v>121</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.441</v>
+        <v>0.87</v>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>Christopher Evans, Olivia Fischer, Matthew Brown</t>
+          <t>Thomas Yamamoto, Amanda Fischer, Michael Vega</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -605,7 +609,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Iris Solutions</t>
+          <t>Echo Holdings</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -615,45 +619,41 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2011-10-15</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>2014-09-06</t>
-        </is>
-      </c>
+          <t>2011-02-04</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="n">
-        <v>1128.4</v>
+        <v>1339.3</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1307.4</v>
+        <v/>
       </c>
       <c r="I6" s="4" t="n">
-        <v>205.4</v>
+        <v>127.2</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>315.1</v>
+        <v/>
       </c>
       <c r="K6" s="4" t="n">
-        <v>310.9</v>
+        <v>65.5</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.534</v>
+        <v>0.357</v>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>Michael Xu, Mark Vega, Ravi Davis</t>
+          <t>Wei Anderson, Wei Rossi, Matthew Qureshi</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -665,17 +665,17 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Cobalt Health</t>
+          <t>Echo Media</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -685,35 +685,35 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2010-02-04</t>
+          <t>2011-10-12</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2015-12-08</t>
+          <t>2016-11-01</t>
         </is>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1528.6</v>
+        <v>1819.3</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3595.5</v>
+        <v>3818.4</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>181.7</v>
+        <v>387.7</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>413.5</v>
+        <v>662.6</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>196.8</v>
+        <v>1658.7</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.412</v>
+        <v>0.635</v>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>Sophie Lopez, David Rossi, Thomas Tanaka, Olivia Nakamura, Robert Ueno</t>
+          <t>Robert Kim, Thomas Williams</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -725,55 +725,51 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Fathom Networks</t>
+          <t>Fathom Bio</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2013-02-15</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>2020-02-02</t>
-        </is>
-      </c>
+          <t>2012-04-10</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="n">
-        <v>574.9</v>
+        <v>159.7</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1184.8</v>
+        <v/>
       </c>
       <c r="I8" s="4" t="n">
-        <v>144.1</v>
+        <v>25.6</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>350.2</v>
+        <v/>
       </c>
       <c r="K8" s="4" t="n">
-        <v>533.5</v>
+        <v>29.3</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.223</v>
+        <v>0.624</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>Matthew Evans, Ravi Fischer, Priya Mueller</t>
+          <t>Priya Hassan, Thomas Johnson, Ravi Vega</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -785,51 +781,55 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Radial Tech</t>
+          <t>Nimbus Corp</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2013-09-02</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr"/>
+          <t>2013-02-12</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>2016-01-30</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="n">
-        <v>146.7</v>
+        <v>1023.5</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v/>
+        <v>1906.1</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>30.2</v>
+        <v>210.4</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v/>
+        <v>370.2</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>27.2</v>
+        <v>906.2</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.845</v>
+        <v>0.664</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Thomas Evans, Elena Kim, Hannah Ueno, Sarah Lopez, Wei Davis</t>
+          <t>Sophie Zhang, Sarah Evans, Wei Xu, Matthew Schmidt, Mark Williams</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -841,51 +841,55 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Gravity AG</t>
+          <t>Iris Foods</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2010-06-21</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr"/>
+          <t>2012-07-12</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>2016-09-27</t>
+        </is>
+      </c>
       <c r="G10" s="4" t="n">
-        <v>1964.6</v>
+        <v>1715.8</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v/>
+        <v>4965.9</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>472.6</v>
+        <v>342</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v/>
+        <v>409.1</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1426.6</v>
+        <v>1191.1</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.859</v>
+        <v>0.589</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Matthew Anderson, Matthew Ueno</t>
+          <t>Amanda Johnson, Olivia Xu</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -897,7 +901,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Mosaic Foods</t>
+          <t>Echo Systems</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -907,7 +911,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -917,35 +921,35 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2013-11-21</t>
+          <t>2012-06-10</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2019-10-28</t>
+          <t>2018-05-05</t>
         </is>
       </c>
       <c r="G11" s="4" t="n">
-        <v>995.4</v>
+        <v>893.8</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2197</v>
+        <v>660.6</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>156.2</v>
+        <v>219</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>363.8</v>
+        <v>352.7</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>576.3</v>
+        <v>256</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.633</v>
+        <v>0.677</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>Matthew Schmidt, Thomas Yamamoto, Mark Vega</t>
+          <t>Elena Kim, Thomas Hassan, Amanda Brown, Wei Yamamoto</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -957,17 +961,17 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Krypton Dynamics</t>
+          <t>Wavelength Networks</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -977,35 +981,35 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2010-06-15</t>
+          <t>2012-03-27</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2014-06-02</t>
+          <t>2016-02-21</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>276.7</v>
+        <v>1297.5</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>476</v>
+        <v>1969.1</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>42.8</v>
+        <v>131.2</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>98.90000000000001</v>
+        <v>197.7</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>124.4</v>
+        <v>208.9</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.429</v>
+        <v>0.16</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Sarah Evans, Sarah Chen, Andrew Rossi, Sophie Ivanov</t>
+          <t>Ahmed Tanaka, Christopher Yamamoto</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1017,17 +1021,17 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Indigo Tech</t>
+          <t>Forge Group</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1037,35 +1041,35 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2010-07-01</t>
+          <t>2011-06-13</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2015-04-04</t>
+          <t>2016-03-19</t>
         </is>
       </c>
       <c r="G13" s="4" t="n">
-        <v>90.90000000000001</v>
+        <v>401.1</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>269</v>
+        <v>1043.3</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>24.1</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>34.9</v>
+        <v>153</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>54.1</v>
+        <v>164.1</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.629</v>
+        <v>0.699</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>Priya Schmidt, James Rossi</t>
+          <t>Laura Hassan, Laura Chen</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1077,17 +1081,17 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Tessera Capital</t>
+          <t>Apex Group</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1097,35 +1101,35 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2012-07-08</t>
+          <t>2012-06-03</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2018-09-02</t>
+          <t>2019-03-16</t>
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1068.9</v>
+        <v>802.6</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>997</v>
+        <v>2107.4</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>174.4</v>
+        <v>81.5</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>254.6</v>
+        <v>169.7</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>412.6</v>
+        <v>142.7</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.414</v>
+        <v>0.613</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>Emma Lopez, Yuki Kim, Ravi Williams, Ahmed Vega, Priya Zhang</t>
+          <t>Olivia Anderson, Ravi Yamamoto, Yuki Mueller</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -1137,55 +1141,51 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Delta Ltd</t>
+          <t>Fathom Dynamics</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2013-07-21</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>2018-09-08</t>
-        </is>
-      </c>
+          <t>2011-04-04</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="n">
-        <v>1218.6</v>
+        <v>1731.2</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2958.1</v>
+        <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>326.1</v>
+        <v>392.6</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>266.4</v>
+        <v/>
       </c>
       <c r="K15" s="4" t="n">
-        <v>532.3</v>
+        <v>1169.5</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.877</v>
+        <v>0.264</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Sophie Hassan, Hannah Ueno</t>
+          <t>Ravi Anderson, Olivia Kim, Mark Lopez, Hannah Kim, Amanda Patel</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -1197,77 +1197,73 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Meridian Partners</t>
+          <t>Nova Partners</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>2021-07-28</t>
-        </is>
-      </c>
+          <t>2011-07-15</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="n">
-        <v>1362.2</v>
+        <v>1257.7</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3227.9</v>
+        <v/>
       </c>
       <c r="I16" s="4" t="n">
-        <v>210.4</v>
+        <v>303.3</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>282.6</v>
+        <v/>
       </c>
       <c r="K16" s="4" t="n">
-        <v>256.8</v>
+        <v>420.5</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.971</v>
+        <v>0.441</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>Jessica Ueno, Olivia Yamamoto, Wei Davis</t>
+          <t>Andrew Xu, Christopher Ueno</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>Fund II</t>
+          <t>Fund I</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Apex Labs</t>
+          <t>Beacon Partners</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1277,35 +1273,35 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2014-07-01</t>
+          <t>2013-05-04</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2018-06-14</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1964.6</v>
+        <v>348.8</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3796.8</v>
+        <v>620.4</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>396</v>
+        <v>47.5</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>394.8</v>
+        <v>79.5</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1603.6</v>
+        <v>210.5</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.304</v>
+        <v>0.461</v>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>Ahmed Gupta, James Fischer, Jessica Anderson, James Lopez, Priya Gupta</t>
+          <t>Mark Nakamura, Hannah Brown, Wei Qureshi, Christopher Fischer</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -1317,17 +1313,17 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Atlas Bio</t>
+          <t>Nimbus SA</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1337,35 +1333,35 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2015-03-16</t>
+          <t>2012-11-28</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2020-12-19</t>
+          <t>2016-01-22</t>
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1859</v>
+        <v>1604.9</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2056.3</v>
+        <v>2891.7</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>512.9</v>
+        <v>333.4</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>580.2</v>
+        <v>524.8</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1708.7</v>
+        <v>1134.7</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.279</v>
+        <v>0.207</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Olivia Schmidt, Jennifer Tanaka, Elena Qureshi</t>
+          <t>Thomas Ueno, Andrew Fischer, Elena Xu, Christopher Tanaka, Matthew Kim</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -1377,17 +1373,17 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Radial Solutions</t>
+          <t>Tessera Capital</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1397,35 +1393,35 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2012-07-27</t>
+          <t>2014-10-26</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>2018-10-15</t>
+          <t>2018-08-25</t>
         </is>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1611.4</v>
+        <v>658.4</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2091.7</v>
+        <v>1258.1</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>296.2</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>288.3</v>
+        <v>132.3</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>761.1</v>
+        <v>291.4</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.991</v>
+        <v>0.304</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>Olivia Rossi, Wei Davis</t>
+          <t>Wei Lopez, Christopher Lopez, Yuki Evans</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -1437,7 +1433,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Stratus Networks</t>
+          <t>Kepler SA</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -1447,7 +1443,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1457,35 +1453,35 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2013-10-08</t>
+          <t>2015-10-01</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2019-12-07</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1677.5</v>
+        <v>1625</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3815.6</v>
+        <v>4931.7</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>165.3</v>
+        <v>415.6</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>398.2</v>
+        <v>626.5</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>737.9</v>
+        <v>282.1</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.229</v>
+        <v>0.336</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>Andrew Johnson, Thomas Yamamoto, James Patel, James Johnson, Priya Yamamoto</t>
+          <t>Olivia Vega, Jennifer Kim, Jessica Gupta</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -1497,51 +1493,55 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Tessera Logic</t>
+          <t>Fathom Health</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2015-01-08</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr"/>
+          <t>2014-09-15</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>2020-07-26</t>
+        </is>
+      </c>
       <c r="G21" s="4" t="n">
-        <v>497.7</v>
+        <v>533</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v/>
+        <v>1733.2</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>110.3</v>
+        <v>145.3</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v/>
+        <v>116.7</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>56.8</v>
+        <v>197.8</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.346</v>
+        <v>0.862</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>Hannah Davis, Rachel Evans, Christopher Anderson, Amanda Gupta</t>
+          <t>David Hassan, Robert Lopez, David Kim, Ahmed Johnson, Emma Ueno</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -1553,17 +1553,17 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Wavelength Networks</t>
+          <t>Polaris Networks</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1573,57 +1573,57 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2016-04-12</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1350.5</v>
+        <v>197.5</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1910.6</v>
+        <v>597.4</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>339</v>
+        <v>36.9</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>720.5</v>
+        <v>74.3</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>186.3</v>
+        <v>69.2</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.6</v>
+        <v>0.696</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>Hannah Patel, Rachel Zhang, Andrew Mueller, Amanda Xu, Matthew Brown</t>
+          <t>Thomas Brown, Ravi Kim, Ahmed Ivanov, Jennifer Ueno</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>Fund III</t>
+          <t>Fund II</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Radial Labs</t>
+          <t>Ember SA</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1633,57 +1633,57 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>2016-11-09</t>
+          <t>2013-11-27</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2021-08-12</t>
+          <t>2018-12-11</t>
         </is>
       </c>
       <c r="G23" s="4" t="n">
-        <v>483.6</v>
+        <v>827.6</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1072.3</v>
+        <v>2230</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>73.5</v>
+        <v>179</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>136.3</v>
+        <v>201.2</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>257.3</v>
+        <v>278.4</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.969</v>
+        <v>0.491</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>Ravi Nakamura, Yuki Williams, Laura Kim, Olivia Vega, Hannah Brown</t>
+          <t>James Evans, Thomas Anderson, Michael Patel, Daniel Nakamura, Ahmed Johnson</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>Fund III</t>
+          <t>Fund II</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Iris Capital</t>
+          <t>Radial GmbH</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1693,57 +1693,57 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2017-06-25</t>
+          <t>2015-06-26</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2022-06-05</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1457.2</v>
+        <v>246.9</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1600</v>
+        <v>556.5</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>242.6</v>
+        <v>40.5</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>578.2</v>
+        <v>43.4</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>905.3</v>
+        <v>99</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.371</v>
+        <v>0.373</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Hannah Zhang, Thomas Mueller, Rachel Johnson</t>
+          <t>Matthew Anderson, Thomas Tanaka, Emma Evans, Laura Chen, Priya Rossi</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>Fund III</t>
+          <t>Fund II</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Forge Media</t>
+          <t>Drift Media</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1753,57 +1753,57 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>2015-04-27</t>
+          <t>2013-09-02</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>2021-02-07</t>
+          <t>2016-06-19</t>
         </is>
       </c>
       <c r="G25" s="4" t="n">
-        <v>992.3</v>
+        <v>1316</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>733.7</v>
+        <v>2981.7</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>133.3</v>
+        <v>171.1</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>290.2</v>
+        <v>359.1</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>494.4</v>
+        <v>348.1</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.774</v>
+        <v>0.338</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Ahmed Vega, Robert Tanaka, Andrew Ueno, David Davis</t>
+          <t>Ahmed Tanaka, Jennifer Mueller, Ravi Rossi, David Brown</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>Fund III</t>
+          <t>Fund II</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Lattice Ltd</t>
+          <t>Ember GmbH</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1813,57 +1813,57 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2014-09-25</t>
+          <t>2015-07-24</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>2018-09-27</t>
+          <t>2019-10-15</t>
         </is>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1511.7</v>
+        <v>928.8</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1195.9</v>
+        <v>2224.6</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>215.8</v>
+        <v>194.2</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>247.3</v>
+        <v>432.4</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>744</v>
+        <v>601.9</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.389</v>
+        <v>0.332</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Robert Hassan, Jessica Patel, David Anderson, Olivia Tanaka</t>
+          <t>Thomas Patel, Christopher O'Brien, Emma Gupta, Sarah Kim, Christopher Johnson</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>Fund III</t>
+          <t>Fund II</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Nova Capital</t>
+          <t>Beacon Ltd</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1873,113 +1873,117 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>2015-07-15</t>
+          <t>2012-12-23</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>2022-09-30</t>
+          <t>2019-10-13</t>
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>697.3</v>
+        <v>1647.6</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1148.4</v>
+        <v>1774.9</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>126.4</v>
+        <v>460.5</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>312.6</v>
+        <v>1072.6</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>282.5</v>
+        <v>1815.6</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.645</v>
+        <v>0.318</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>James Chen, Sophie Kim, Michael Hassan</t>
+          <t>Priya Johnson, Sophie Evans, Elena Fischer, Daniel Chen, Ahmed Rossi</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>Fund III</t>
+          <t>Fund II</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Orion GmbH</t>
+          <t>Umbra Solutions</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2016-10-10</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr"/>
+          <t>2015-01-18</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>2020-04-03</t>
+        </is>
+      </c>
       <c r="G28" s="4" t="n">
-        <v>565.1</v>
+        <v>1071.4</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v/>
+        <v>3422.1</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>126.9</v>
+        <v>158.9</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v/>
+        <v>155.5</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>64.90000000000001</v>
+        <v>481.8</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.238</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>Hannah Fischer, Michael Fischer, Sarah Patel, Mark Qureshi</t>
+          <t>Priya Qureshi, Matthew Lopez, Ravi Johnson, Rachel Williams</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>Fund III</t>
+          <t>Fund II</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Polaris Tech</t>
+          <t>Stratus Tech</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1989,35 +1993,35 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>2015-03-16</t>
+          <t>2017-09-12</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2022-08-19</t>
         </is>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1937.4</v>
+        <v>1225.5</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1670.2</v>
+        <v>3806</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>327.9</v>
+        <v>269.5</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>736.4</v>
+        <v>468.6</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1448.4</v>
+        <v>416.6</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.331</v>
+        <v>0.165</v>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Andrew Hassan, Emma Mueller, Christopher Fischer, Andrew Williams, Yuki Nakamura</t>
+          <t>Jennifer Patel, Jessica Ivanov, Emma Schmidt, Ravi Chen, Wei Tanaka</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -2029,17 +2033,17 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Echo Networks</t>
+          <t>Atlas Materials</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -2049,35 +2053,35 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2015-11-19</t>
+          <t>2016-08-24</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>2020-09-12</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="G30" s="4" t="n">
-        <v>387.7</v>
+        <v>55.7</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>886.1</v>
+        <v>134.4</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>41.7</v>
+        <v>6.2</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>93.8</v>
+        <v>14.4</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>126.9</v>
+        <v>19.7</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.42</v>
+        <v>0.462</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Rachel Mueller, Mark Zhang, Jessica Nakamura, Priya Patel</t>
+          <t>Laura Chen, Andrew Schmidt, Jennifer Rossi</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -2089,17 +2093,17 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Orion Corp</t>
+          <t>Cipher Energy</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2109,57 +2113,57 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>2017-12-06</t>
+          <t>2015-09-06</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>2023-02-13</t>
+          <t>2019-09-07</t>
         </is>
       </c>
       <c r="G31" s="4" t="n">
-        <v>497.5</v>
+        <v>1261.7</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1485</v>
+        <v>2460</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>115.5</v>
+        <v>277.1</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>117.3</v>
+        <v>236.1</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>368.5</v>
+        <v>1111.1</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.419</v>
+        <v>0.727</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Ahmed Yamamoto, Andrew Johnson, Emma Lopez</t>
+          <t>David Tanaka, Ravi Ivanov</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>Fund IV</t>
+          <t>Fund III</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Iris Systems</t>
+          <t>Meridian Networks</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -2169,57 +2173,57 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2018-05-02</t>
+          <t>2016-06-13</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2019-03-17</t>
         </is>
       </c>
       <c r="G32" s="4" t="n">
-        <v>622.5</v>
+        <v>463.2</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>2083.7</v>
+        <v>435.8</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>133.9</v>
+        <v>112.3</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>322.9</v>
+        <v>183.5</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>474.8</v>
+        <v>453.3</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.578</v>
+        <v>0.539</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>Ravi Fischer, Andrew Nakamura, Christopher Gupta, Christopher Gupta, Matthew Mueller</t>
+          <t>James Fischer, Ahmed Patel</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>Fund IV</t>
+          <t>Fund III</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Drift SA</t>
+          <t>Xenith AG</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2229,57 +2233,57 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>2019-06-02</t>
+          <t>2017-08-18</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1028.7</v>
+        <v>1756.2</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1091.7</v>
+        <v>2813.1</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>251.9</v>
+        <v>466.6</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>426.3</v>
+        <v>688.7</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>816.9</v>
+        <v>1362.8</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.526</v>
+        <v>0.876</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>Daniel Yamamoto, Daniel Kim, Robert Vega, Robert Yamamoto, Ahmed Yamamoto</t>
+          <t>Sophie Ueno, Jessica Davis, Laura Brown, Jessica Fischer</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>Fund IV</t>
+          <t>Fund III</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Quanta Energy</t>
+          <t>Wavelength Industries</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -2289,57 +2293,57 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2016-11-16</t>
+          <t>2014-01-24</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2018-12-04</t>
         </is>
       </c>
       <c r="G34" s="4" t="n">
-        <v>69.3</v>
+        <v>702.5</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>144.3</v>
+        <v>819.9</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>10</v>
+        <v>134.4</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>19.5</v>
+        <v>221.1</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>20.2</v>
+        <v>315.6</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.446</v>
+        <v>0.869</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>Wei Johnson, Rachel Mueller, Emma Anderson</t>
+          <t>Thomas Xu, Amanda Kim, Andrew Fischer, Hannah Schmidt</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>Fund IV</t>
+          <t>Fund III</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Polaris Materials</t>
+          <t>Umbra Foods</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2349,57 +2353,57 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>2018-09-25</t>
+          <t>2014-03-02</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2017-05-29</t>
         </is>
       </c>
       <c r="G35" s="4" t="n">
-        <v>954.8</v>
+        <v>177</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>2761.5</v>
+        <v>538.5</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>133.8</v>
+        <v>21</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>291.7</v>
+        <v>34.7</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>229.7</v>
+        <v>39.4</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.452</v>
+        <v>0.243</v>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>Christopher Evans, James Kim</t>
+          <t>Amanda Davis, Thomas Brown, Robert O'Brien, Daniel Davis</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>Fund IV</t>
+          <t>Fund III</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Atlas Labs</t>
+          <t>Echo Energy</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2409,57 +2413,57 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>2018-12-18</t>
+          <t>2014-02-28</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>2022-03-07</t>
+          <t>2020-04-14</t>
         </is>
       </c>
       <c r="G36" s="4" t="n">
-        <v>849</v>
+        <v>1638.1</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>2050.9</v>
+        <v>1685.9</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>152.9</v>
+        <v>304.5</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>305.6</v>
+        <v>387.8</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>182.1</v>
+        <v>470</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.742</v>
+        <v>0.514</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>Amanda Kim, Elena Fischer</t>
+          <t>Robert O'Brien, Elena Johnson</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>Fund IV</t>
+          <t>Fund III</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Lattice Systems</t>
+          <t>Tessera GmbH</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2469,57 +2473,57 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>2019-04-20</t>
+          <t>2015-01-22</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2018-01-13</t>
         </is>
       </c>
       <c r="G37" s="4" t="n">
-        <v>95.2</v>
+        <v>238.9</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>240.8</v>
+        <v>744.3</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>24.8</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>27.8</v>
+        <v>91.5</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>59.4</v>
+        <v>56.7</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.211</v>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>Wei Johnson, Yuki Williams, James Chen, Olivia Ivanov</t>
+          <t>David Lopez, Sophie Hassan, Michael Mueller, Daniel Nakamura</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>Fund IV</t>
+          <t>Fund III</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Bloom Health</t>
+          <t>Junction Tech</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2529,35 +2533,35 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2018-11-14</t>
+          <t>2018-12-28</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>2024-12-29</t>
+          <t>2025-02-16</t>
         </is>
       </c>
       <c r="G38" s="4" t="n">
-        <v>717</v>
+        <v>623.8</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1651.9</v>
+        <v>496.3</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>178.2</v>
+        <v>165.4</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>235.7</v>
+        <v>250.3</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>748.4</v>
+        <v>348.6</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.742</v>
+        <v>0.404</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>Olivia Johnson, Yuki Ueno, Michael Qureshi, Ravi Gupta, Emma Schmidt</t>
+          <t>Priya Tanaka, David Kim</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -2569,17 +2573,17 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Drift Logic</t>
+          <t>Orion Materials</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2589,35 +2593,35 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>2017-09-17</t>
+          <t>2018-06-20</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="G39" s="4" t="n">
-        <v>466.6</v>
+        <v>900.5</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>694.1</v>
+        <v>1525.4</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>57.4</v>
+        <v>103.4</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>137.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>185.4</v>
+        <v>250.6</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>0.76</v>
+        <v>0.195</v>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>Jessica Vega, Emma Patel, Emma Ueno, Matthew Chen, Olivia O'Brien</t>
+          <t>James Zhang, James Lopez</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -2629,7 +2633,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Stratus Inc</t>
+          <t>Halo GmbH</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -2639,7 +2643,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2649,53 +2653,53 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2019-03-01</t>
+          <t>2016-07-08</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="n">
-        <v>605.4</v>
+        <v>1480.6</v>
       </c>
       <c r="H40" s="4" t="n">
         <v/>
       </c>
       <c r="I40" s="4" t="n">
-        <v>83.40000000000001</v>
+        <v>295.1</v>
       </c>
       <c r="J40" s="4" t="n">
         <v/>
       </c>
       <c r="K40" s="4" t="n">
-        <v>131.2</v>
+        <v>167.3</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.994</v>
+        <v>0.514</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>James Schmidt, Olivia Tanaka, Wei Vega, Jessica Lopez, Rachel Evans</t>
+          <t>Rachel Ivanov, Ravi Mueller, Robert Yamamoto, Andrew Lopez, Daniel Yamamoto</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>Fund V</t>
+          <t>Fund IV</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Nova Energy</t>
+          <t>Atlas Networks</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2705,113 +2709,117 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>2020-03-19</t>
+          <t>2018-06-16</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="G41" s="4" t="n">
-        <v>912.4</v>
+        <v>1567.8</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>681.5</v>
+        <v>3492.4</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>220.8</v>
+        <v>414.4</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>492.9</v>
+        <v>797.1</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>915.6</v>
+        <v>1855.4</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>0.59</v>
+        <v>0.769</v>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>Wei Anderson, Andrew Chen</t>
+          <t>Elena Nakamura, Michael Ueno, Sophie Hassan, Andrew Vega, Daniel Davis</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>Fund V</t>
+          <t>Fund IV</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Radial GmbH</t>
+          <t>Yields Health</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr"/>
+          <t>2017-11-28</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>2020-10-21</t>
+        </is>
+      </c>
       <c r="G42" s="4" t="n">
-        <v>1884.7</v>
+        <v>1103.1</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v/>
+        <v>2949.8</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>294.9</v>
+        <v>195.7</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v/>
+        <v>460.3</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>1135</v>
+        <v>103.5</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.29</v>
+        <v>0.987</v>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>James Schmidt, Matthew Lopez, Yuki Kim</t>
+          <t>David Brown, Thomas Johnson, Wei Ueno, Sophie Johnson, Matthew Tanaka</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>Fund V</t>
+          <t>Fund IV</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Delta Pharma</t>
+          <t>Nimbus Capital</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2821,117 +2829,113 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>2018-06-11</t>
+          <t>2017-07-17</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>2021-04-27</t>
+          <t>2020-05-31</t>
         </is>
       </c>
       <c r="G43" s="4" t="n">
-        <v>112</v>
+        <v>1241.8</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>308.3</v>
+        <v>2552.8</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>11.1</v>
+        <v>334.9</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>18.4</v>
+        <v>477.2</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>35.6</v>
+        <v>489.9</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>0.631</v>
+        <v>0.86</v>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>Ahmed Mueller, Jessica Mueller, Ravi Patel, Jennifer Brown</t>
+          <t>Thomas Rossi, Olivia Zhang</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>Fund V</t>
+          <t>Fund IV</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Gravity Pharma</t>
+          <t>Yields Partners</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2019-08-17</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>2025-08-16</t>
-        </is>
-      </c>
+          <t>2019-12-02</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="n">
-        <v>481.1</v>
+        <v>240.7</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>1288.9</v>
+        <v/>
       </c>
       <c r="I44" s="4" t="n">
-        <v>114</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>139.9</v>
+        <v/>
       </c>
       <c r="K44" s="4" t="n">
-        <v>340</v>
+        <v>233.1</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.707</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>Laura Gupta, David Tanaka, Ahmed Anderson, Amanda Brown</t>
+          <t>Thomas Mueller, Sophie Tanaka</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>Fund V</t>
+          <t>Fund IV</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Tessera Media</t>
+          <t>Halo Energy</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2941,91 +2945,95 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>2019-03-03</t>
+          <t>2019-08-05</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="G45" s="4" t="n">
-        <v>1340.8</v>
+        <v>1225.9</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>4028.4</v>
+        <v>1913.2</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>344</v>
+        <v>278.8</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>605.6</v>
+        <v>647.8</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>576.8</v>
+        <v>524.9</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>0.718</v>
+        <v>0.261</v>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>David Chen, Ahmed Williams, Matthew Ivanov, Amanda Schmidt</t>
+          <t>Michael Vega, Jennifer Fischer</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>Fund V</t>
+          <t>Fund IV</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Umbra Solutions</t>
+          <t>Delta Systems</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>2020-08-01</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr"/>
+          <t>2021-11-05</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
       <c r="G46" s="4" t="n">
-        <v>1429.5</v>
+        <v>971.4</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v/>
+        <v>831.9</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>268.5</v>
+        <v>162.2</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v/>
+        <v>277</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>414.5</v>
+        <v>253.2</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.336</v>
+        <v>0.306</v>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>James Ueno, Michael O'Brien</t>
+          <t>Jennifer Fischer, Sophie Xu, James Xu</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -3037,12 +3045,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Wavelength Systems</t>
+          <t>Lumen Partners</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -3057,35 +3065,35 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
+          <t>2019-12-10</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="G47" s="4" t="n">
-        <v>1384.1</v>
+        <v>629.2</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>2985.1</v>
+        <v>2060.3</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>264.6</v>
+        <v>156</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>513.2</v>
+        <v>239.1</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>1070</v>
+        <v>258.9</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>0.445</v>
+        <v>0.207</v>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>Ahmed Nakamura, Amanda Qureshi, Emma O'Brien</t>
+          <t>Sophie Patel, Jessica Qureshi</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -3097,17 +3105,17 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Indigo Networks</t>
+          <t>Drift Inc</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -3117,35 +3125,35 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2019-05-23</t>
+          <t>2021-01-09</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="G48" s="4" t="n">
-        <v>1961.7</v>
+        <v>1232.9</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>3298.7</v>
+        <v>1566.2</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>406.3</v>
+        <v>111.9</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>932.3</v>
+        <v>225.5</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>1656.4</v>
+        <v>204.5</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>0.437</v>
+        <v>0.964</v>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>Olivia Ivanov, Jennifer Tanaka, Thomas Patel, Olivia Rossi, Andrew Davis</t>
+          <t>Sophie Yamamoto, Thomas Anderson, Ahmed Kim, Emma Ueno, Robert Nakamura</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -3157,17 +3165,17 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Glacier Logic</t>
+          <t>Bloom Holdings</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -3177,35 +3185,35 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>2020-05-04</t>
+          <t>2019-05-26</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2022-07-15</t>
         </is>
       </c>
       <c r="G49" s="4" t="n">
-        <v>367</v>
+        <v>1994.5</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>568.3</v>
+        <v>4654.2</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>76.2</v>
+        <v>211.9</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>116.9</v>
+        <v>498.4</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>76.09999999999999</v>
+        <v>239.4</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>0.736</v>
+        <v>0.798</v>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>Amanda Vega, James Rossi, Andrew Anderson, Christopher Ueno, Jennifer Nakamura</t>
+          <t>Hannah Lopez, Olivia Zhang, James Ueno</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -3217,17 +3225,17 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Yields Networks</t>
+          <t>Vertex Holdings</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -3237,35 +3245,35 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
+          <t>2019-10-18</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="G50" s="4" t="n">
-        <v>325.6</v>
+        <v>939.1</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>289.7</v>
+        <v>1307.3</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>55.4</v>
+        <v>147</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>85.90000000000001</v>
+        <v>201.3</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>129.2</v>
+        <v>586</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.736</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>Priya Mueller, Ahmed Tanaka</t>
+          <t>Matthew Gupta, Andrew O'Brien, Michael Ueno, Amanda O'Brien</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -3277,7 +3285,7 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Cipher AG</t>
+          <t>Drift Capital</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -3287,41 +3295,45 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>2020-10-13</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr"/>
+          <t>2020-04-14</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>2023-07-03</t>
+        </is>
+      </c>
       <c r="G51" s="4" t="n">
-        <v>1805</v>
+        <v>275.7</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v/>
+        <v>718.9</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>158.5</v>
+        <v>71</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v/>
+        <v>61.6</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>153.7</v>
+        <v>212</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>0.318</v>
+        <v>0.851</v>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>Christopher Anderson, Daniel Zhang</t>
+          <t>Robert Rossi, Jessica Chen</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -3333,17 +3345,17 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Forge Tech</t>
+          <t>Vertex Labs</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -3353,35 +3365,35 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2020-08-09</t>
+          <t>2020-10-17</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="G52" s="4" t="n">
-        <v>182.1</v>
+        <v>1491.3</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>513.7</v>
+        <v>1792.3</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>40.1</v>
+        <v>335.6</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>81.09999999999999</v>
+        <v>327.3</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>88.3</v>
+        <v>456.9</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>0.571</v>
+        <v>0.27</v>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>Robert Chen, Elena Vega, Hannah Lopez</t>
+          <t>Ravi Gupta, Rachel O'Brien</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -3393,51 +3405,55 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Beacon Ltd</t>
+          <t>Meridian Materials</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr"/>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>2023-05-09</t>
+        </is>
+      </c>
       <c r="G53" s="4" t="n">
-        <v>1517.4</v>
+        <v>478.4</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v/>
+        <v>508.8</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>192.8</v>
+        <v>91.8</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v/>
+        <v>180.8</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>782</v>
+        <v>123.1</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>0.486</v>
+        <v>0.57</v>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>Wei Kim, Priya Yamamoto, Michael Hassan, Ahmed Gupta, Wei Nakamura</t>
+          <t>David Ueno, Thomas O'Brien</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -3449,51 +3465,55 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Yields Ltd</t>
+          <t>Halo Dynamics</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2019-09-13</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr"/>
+          <t>2018-03-26</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
       <c r="G54" s="4" t="n">
-        <v>1203.9</v>
+        <v>1777.6</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v/>
+        <v>3945.7</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>292</v>
+        <v>480.9</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v/>
+        <v>1065.8</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>916.7</v>
+        <v>1329.8</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>0.792</v>
+        <v>0.769</v>
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t>Christopher Rossi, Sarah Williams, Emma Schmidt, Matthew Ueno</t>
+          <t>Andrew Anderson, Amanda Hassan, Elena Lopez, Thomas Hassan, Priya Ueno</t>
         </is>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -3505,17 +3525,17 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Delta Systems</t>
+          <t>Halo Labs</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -3525,35 +3545,35 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>2018-03-11</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>2021-04-19</t>
+          <t>2024-08-31</t>
         </is>
       </c>
       <c r="G55" s="4" t="n">
-        <v>1662.6</v>
+        <v>1371</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>3084</v>
+        <v>1898.1</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>411.2</v>
+        <v>191.4</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>782.7</v>
+        <v>188</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>345.9</v>
+        <v>214.5</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>0.679</v>
+        <v>0.287</v>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>David Patel, Ravi Kim, Amanda Vega</t>
+          <t>Priya Gupta, Ravi Tanaka, Olivia Ueno, Thomas Gupta</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -3565,7 +3585,7 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Helix Ltd</t>
+          <t>Cobalt Logistics</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -3575,7 +3595,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -3585,35 +3605,35 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>2018-03-28</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>2022-05-10</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="G56" s="4" t="n">
-        <v>911.6</v>
+        <v>1172.7</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>1113</v>
+        <v>1544.2</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>235.9</v>
+        <v>220.3</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>236.3</v>
+        <v>412.8</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>634.2</v>
+        <v>757.6</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.664</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>James O'Brien, Laura Patel</t>
+          <t>Olivia Evans, Jennifer Kim, Ahmed Nakamura, Laura Patel, Emma Hassan</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -3625,17 +3645,17 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Mosaic Dynamics</t>
+          <t>Delta Group</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3645,35 +3665,35 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>2021-01-08</t>
+          <t>2020-10-27</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-01-12</t>
         </is>
       </c>
       <c r="G57" s="4" t="n">
-        <v>879.3</v>
+        <v>546.7</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>1974.2</v>
+        <v>383.9</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>88.40000000000001</v>
+        <v>141.4</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>121.3</v>
+        <v>212.8</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>138.9</v>
+        <v>246.9</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>0.394</v>
+        <v>0.481</v>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>Rachel Chen, Priya Ivanov, Priya Mueller, Hannah Nakamura</t>
+          <t>Jessica Davis, Amanda Hassan</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -3685,17 +3705,17 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Tessera Labs</t>
+          <t>Cipher SA</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3705,35 +3725,35 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2019-10-11</t>
+          <t>2018-07-24</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>2022-09-28</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="G58" s="4" t="n">
-        <v>1344.8</v>
+        <v>1718.1</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>2670.7</v>
+        <v>4746</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>139.4</v>
+        <v>382.9</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>160.4</v>
+        <v>725.5</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>276</v>
+        <v>638</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>0.759</v>
+        <v>0.493</v>
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>Olivia Schmidt, Ravi Tanaka</t>
+          <t>Elena Nakamura, Wei Ueno</t>
         </is>
       </c>
       <c r="N58" s="4" t="inlineStr">
@@ -3745,17 +3765,17 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Orion Energy</t>
+          <t>Gravity Inc</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3765,35 +3785,35 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2019-05-03</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="G59" s="4" t="n">
-        <v>779.6</v>
+        <v>523.3</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>1118.5</v>
+        <v>786.1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>135.1</v>
+        <v>123.9</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>238.6</v>
+        <v>256.1</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>135.8</v>
+        <v>367.3</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>0.704</v>
+        <v>0.327</v>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>Michael Schmidt, Mark Lopez, Ahmed Hassan</t>
+          <t>Emma O'Brien, Sarah Nakamura, Matthew Hassan, Daniel Davis</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -3805,17 +3825,17 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Cobalt AG</t>
+          <t>Mosaic Corp</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -3825,35 +3845,35 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>2020-11-02</t>
+          <t>2018-12-09</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="G60" s="4" t="n">
-        <v>868.8</v>
+        <v>1920.9</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>2296.9</v>
+        <v>4464.6</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>128.6</v>
+        <v>479.4</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>269.9</v>
+        <v>1108.3</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>118.8</v>
+        <v>1900.2</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>0.245</v>
+        <v>0.473</v>
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>Elena Vega, James O'Brien, Jessica Williams, Mark Kim</t>
+          <t>Rachel Schmidt, Michael Rossi, Amanda Lopez, Amanda Qureshi</t>
         </is>
       </c>
       <c r="N60" s="4" t="inlineStr">
@@ -3865,17 +3885,17 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Beacon Capital</t>
+          <t>Orion Bio</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3885,98 +3905,38 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
+          <t>2019-11-21</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>2023-03-21</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="G61" s="4" t="n">
-        <v>393</v>
+        <v>1163</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>578.4</v>
+        <v>2897.3</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>55.8</v>
+        <v>212</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>92.09999999999999</v>
+        <v>486.7</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>231.6</v>
+        <v>910.6</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>0.914</v>
+        <v>0.168</v>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>Laura Anderson, Robert Fischer, Daniel Kim, Michael Lopez, Matthew Zhang</t>
+          <t>Elena Fischer, Mark Nakamura, Priya Johnson, Elena Lopez, Rachel Qureshi</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
-        <is>
-          <t>Fund V</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>Delta Media</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>Toronto, CA</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>2019-03-12</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>2023-02-16</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="n">
-        <v>772.2</v>
-      </c>
-      <c r="H62" s="4" t="n">
-        <v>2457.7</v>
-      </c>
-      <c r="I62" s="4" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="J62" s="4" t="n">
-        <v>122.7</v>
-      </c>
-      <c r="K62" s="4" t="n">
-        <v>187.2</v>
-      </c>
-      <c r="L62" s="4" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="M62" s="4" t="inlineStr">
-        <is>
-          <t>Robert Williams, Jessica Rossi, Yuki Zhang</t>
-        </is>
-      </c>
-      <c r="N62" s="4" t="inlineStr">
         <is>
           <t>Fund V</t>
         </is>
